--- a/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C57848B2-FAF9-4EDF-83F4-0F3D1C5FDBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC4DF532-1132-4390-A448-5A4329380DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -2432,7 +2432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13EB4CD2-EAC9-4467-8FF9-1F3A24B4EE66}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F60C94D4-BA15-40E3-9EDA-A06CE4385BC9}">
   <dimension ref="B2:AF302"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8027,7 +8027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656F0166-D7D8-4AD2-976F-5BB6EE70D081}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACFA93B-878D-4F0C-B459-D942D9142A3C}">
   <dimension ref="B9:L29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20157,7 +20157,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B250F783-399E-4F9D-8134-F3B61C557912}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10E0C0A7-431F-4F0F-98B0-0836D1647071}">
   <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
